--- a/artfynd/A 28052-2024 artfynd.xlsx
+++ b/artfynd/A 28052-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118433745</v>
+        <v>118433170</v>
       </c>
       <c r="B2" t="n">
-        <v>90451</v>
+        <v>91779</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724240</v>
+        <v>724323</v>
       </c>
       <c r="R2" t="n">
-        <v>7347532</v>
+        <v>7347671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118432610</v>
+        <v>118433745</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
+        <v>90451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724298</v>
+        <v>724240</v>
       </c>
       <c r="R3" t="n">
-        <v>7347451</v>
+        <v>7347532</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118433505</v>
+        <v>118433041</v>
       </c>
       <c r="B4" t="n">
-        <v>97867</v>
+        <v>89575</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724216</v>
+        <v>724351</v>
       </c>
       <c r="R4" t="n">
-        <v>7347555</v>
+        <v>7347536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118433002</v>
+        <v>118434082</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>57290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724356</v>
+        <v>724058</v>
       </c>
       <c r="R5" t="n">
-        <v>7347531</v>
+        <v>7347655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,6 +1065,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118433170</v>
+        <v>118432837</v>
       </c>
       <c r="B6" t="n">
-        <v>91779</v>
+        <v>77868</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1108,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724323</v>
+        <v>724298</v>
       </c>
       <c r="R6" t="n">
-        <v>7347671</v>
+        <v>7347451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118433041</v>
+        <v>118433505</v>
       </c>
       <c r="B7" t="n">
-        <v>89575</v>
+        <v>97867</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724351</v>
+        <v>724216</v>
       </c>
       <c r="R7" t="n">
-        <v>7347536</v>
+        <v>7347555</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118432837</v>
+        <v>118433318</v>
       </c>
       <c r="B8" t="n">
-        <v>77868</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724298</v>
+        <v>724240</v>
       </c>
       <c r="R8" t="n">
-        <v>7347451</v>
+        <v>7347597</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118434082</v>
+        <v>118432971</v>
       </c>
       <c r="B9" t="n">
-        <v>57290</v>
+        <v>79073</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,42 +1418,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724058</v>
+        <v>724346</v>
       </c>
       <c r="R9" t="n">
-        <v>7347655</v>
+        <v>7347525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1482,11 +1478,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118432971</v>
+        <v>118433002</v>
       </c>
       <c r="B10" t="n">
-        <v>79073</v>
+        <v>91779</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,25 +1516,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1553,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724346</v>
+        <v>724356</v>
       </c>
       <c r="R10" t="n">
-        <v>7347525</v>
+        <v>7347531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118433318</v>
+        <v>118432610</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,34 +1724,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724240</v>
+        <v>724298</v>
       </c>
       <c r="R12" t="n">
-        <v>7347597</v>
+        <v>7347451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 28052-2024 artfynd.xlsx
+++ b/artfynd/A 28052-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118433170</v>
+        <v>118433002</v>
       </c>
       <c r="B2" t="n">
         <v>91779</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724323</v>
+        <v>724356</v>
       </c>
       <c r="R2" t="n">
-        <v>7347671</v>
+        <v>7347531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118433745</v>
+        <v>118433505</v>
       </c>
       <c r="B3" t="n">
-        <v>90451</v>
+        <v>97867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724240</v>
+        <v>724216</v>
       </c>
       <c r="R3" t="n">
-        <v>7347532</v>
+        <v>7347555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118433041</v>
+        <v>118433318</v>
       </c>
       <c r="B4" t="n">
-        <v>89575</v>
+        <v>78484</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724351</v>
+        <v>724240</v>
       </c>
       <c r="R4" t="n">
-        <v>7347536</v>
+        <v>7347597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118434082</v>
+        <v>118433339</v>
       </c>
       <c r="B5" t="n">
-        <v>57290</v>
+        <v>82263</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724058</v>
+        <v>724253</v>
       </c>
       <c r="R5" t="n">
-        <v>7347655</v>
+        <v>7347552</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1096,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118432837</v>
+        <v>118434082</v>
       </c>
       <c r="B6" t="n">
-        <v>77868</v>
+        <v>57290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724298</v>
+        <v>724058</v>
       </c>
       <c r="R6" t="n">
-        <v>7347451</v>
+        <v>7347655</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,6 +1167,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118433505</v>
+        <v>118433041</v>
       </c>
       <c r="B7" t="n">
-        <v>97867</v>
+        <v>89575</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1210,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724216</v>
+        <v>724351</v>
       </c>
       <c r="R7" t="n">
-        <v>7347555</v>
+        <v>7347536</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118433318</v>
+        <v>118432971</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>79073</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,21 +1316,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724240</v>
+        <v>724346</v>
       </c>
       <c r="R8" t="n">
-        <v>7347597</v>
+        <v>7347525</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118432971</v>
+        <v>118433745</v>
       </c>
       <c r="B9" t="n">
-        <v>79073</v>
+        <v>90451</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,21 +1418,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724346</v>
+        <v>724240</v>
       </c>
       <c r="R9" t="n">
-        <v>7347525</v>
+        <v>7347532</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118433002</v>
+        <v>118432837</v>
       </c>
       <c r="B10" t="n">
-        <v>91779</v>
+        <v>77868</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,25 +1516,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724356</v>
+        <v>724298</v>
       </c>
       <c r="R10" t="n">
-        <v>7347531</v>
+        <v>7347451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118433339</v>
+        <v>118432610</v>
       </c>
       <c r="B11" t="n">
-        <v>82263</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,34 +1622,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724253</v>
+        <v>724298</v>
       </c>
       <c r="R11" t="n">
-        <v>7347552</v>
+        <v>7347451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118432610</v>
+        <v>118433170</v>
       </c>
       <c r="B12" t="n">
-        <v>57290</v>
+        <v>91779</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1720,47 +1729,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724298</v>
+        <v>724323</v>
       </c>
       <c r="R12" t="n">
-        <v>7347451</v>
+        <v>7347671</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 28052-2024 artfynd.xlsx
+++ b/artfynd/A 28052-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118433002</v>
+        <v>118432610</v>
       </c>
       <c r="B2" t="n">
-        <v>91779</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724356</v>
+        <v>724298</v>
       </c>
       <c r="R2" t="n">
-        <v>7347531</v>
+        <v>7347451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118433505</v>
+        <v>118433041</v>
       </c>
       <c r="B3" t="n">
-        <v>97867</v>
+        <v>89582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724216</v>
+        <v>724351</v>
       </c>
       <c r="R3" t="n">
-        <v>7347555</v>
+        <v>7347536</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118433318</v>
+        <v>118432837</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>77875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724240</v>
+        <v>724298</v>
       </c>
       <c r="R4" t="n">
-        <v>7347597</v>
+        <v>7347451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118433339</v>
+        <v>118433170</v>
       </c>
       <c r="B5" t="n">
-        <v>82263</v>
+        <v>91786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724253</v>
+        <v>724323</v>
       </c>
       <c r="R5" t="n">
-        <v>7347552</v>
+        <v>7347671</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1198,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118433041</v>
+        <v>118433002</v>
       </c>
       <c r="B7" t="n">
-        <v>89575</v>
+        <v>91786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1210,25 +1219,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724351</v>
+        <v>724356</v>
       </c>
       <c r="R7" t="n">
-        <v>7347536</v>
+        <v>7347531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118432971</v>
+        <v>118433339</v>
       </c>
       <c r="B8" t="n">
-        <v>79073</v>
+        <v>82270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724346</v>
+        <v>724253</v>
       </c>
       <c r="R8" t="n">
-        <v>7347525</v>
+        <v>7347552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118433745</v>
+        <v>118433505</v>
       </c>
       <c r="B9" t="n">
-        <v>90451</v>
+        <v>97874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,25 +1423,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1451,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724240</v>
+        <v>724216</v>
       </c>
       <c r="R9" t="n">
-        <v>7347532</v>
+        <v>7347555</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118432837</v>
+        <v>118433745</v>
       </c>
       <c r="B10" t="n">
-        <v>77868</v>
+        <v>90458</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1520,21 +1529,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1553,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724298</v>
+        <v>724240</v>
       </c>
       <c r="R10" t="n">
-        <v>7347451</v>
+        <v>7347532</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118432610</v>
+        <v>118432971</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>79080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,43 +1631,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724298</v>
+        <v>724346</v>
       </c>
       <c r="R11" t="n">
-        <v>7347451</v>
+        <v>7347525</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118433170</v>
+        <v>118433318</v>
       </c>
       <c r="B12" t="n">
-        <v>91779</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1729,25 +1729,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724323</v>
+        <v>724240</v>
       </c>
       <c r="R12" t="n">
-        <v>7347671</v>
+        <v>7347597</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 28052-2024 artfynd.xlsx
+++ b/artfynd/A 28052-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118432610</v>
+        <v>118433339</v>
       </c>
       <c r="B2" t="n">
-        <v>57290</v>
+        <v>82270</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724298</v>
+        <v>724253</v>
       </c>
       <c r="R2" t="n">
-        <v>7347451</v>
+        <v>7347552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118432837</v>
+        <v>118432971</v>
       </c>
       <c r="B4" t="n">
-        <v>77875</v>
+        <v>79080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724298</v>
+        <v>724346</v>
       </c>
       <c r="R4" t="n">
-        <v>7347451</v>
+        <v>7347525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118434082</v>
+        <v>118433002</v>
       </c>
       <c r="B6" t="n">
-        <v>57290</v>
+        <v>91786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,46 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724058</v>
+        <v>724356</v>
       </c>
       <c r="R6" t="n">
-        <v>7347655</v>
+        <v>7347531</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1207,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118433002</v>
+        <v>118433745</v>
       </c>
       <c r="B7" t="n">
-        <v>91786</v>
+        <v>90458</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724356</v>
+        <v>724240</v>
       </c>
       <c r="R7" t="n">
-        <v>7347531</v>
+        <v>7347532</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118433339</v>
+        <v>118434082</v>
       </c>
       <c r="B8" t="n">
-        <v>82270</v>
+        <v>57290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,34 +1303,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724253</v>
+        <v>724058</v>
       </c>
       <c r="R8" t="n">
-        <v>7347552</v>
+        <v>7347655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,6 +1371,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118433505</v>
+        <v>118433318</v>
       </c>
       <c r="B9" t="n">
-        <v>97874</v>
+        <v>78491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,25 +1414,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1451,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724216</v>
+        <v>724240</v>
       </c>
       <c r="R9" t="n">
-        <v>7347555</v>
+        <v>7347597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118433745</v>
+        <v>118432610</v>
       </c>
       <c r="B10" t="n">
-        <v>90458</v>
+        <v>57290</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1529,34 +1520,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ridok (Ridok), Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724240</v>
+        <v>724298</v>
       </c>
       <c r="R10" t="n">
-        <v>7347532</v>
+        <v>7347451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118432971</v>
+        <v>118433505</v>
       </c>
       <c r="B11" t="n">
-        <v>79080</v>
+        <v>97874</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,25 +1627,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724346</v>
+        <v>724216</v>
       </c>
       <c r="R11" t="n">
-        <v>7347525</v>
+        <v>7347555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118433318</v>
+        <v>118432837</v>
       </c>
       <c r="B12" t="n">
-        <v>78491</v>
+        <v>77875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1733,21 +1733,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724240</v>
+        <v>724298</v>
       </c>
       <c r="R12" t="n">
-        <v>7347597</v>
+        <v>7347451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 28052-2024 artfynd.xlsx
+++ b/artfynd/A 28052-2024 artfynd.xlsx
@@ -1711,11 +1711,11 @@
         <v>118432610</v>
       </c>
       <c r="B12" t="n">
-        <v>57308</v>
+        <v>57384</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">

--- a/artfynd/A 28052-2024 artfynd.xlsx
+++ b/artfynd/A 28052-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118433339</v>
+        <v>118433745</v>
       </c>
       <c r="B2" t="n">
-        <v>82272</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724253</v>
+        <v>724240</v>
       </c>
       <c r="R2" t="n">
-        <v>7347552</v>
+        <v>7347532</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118432837</v>
+        <v>118433339</v>
       </c>
       <c r="B3" t="n">
-        <v>77877</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724298</v>
+        <v>724253</v>
       </c>
       <c r="R3" t="n">
-        <v>7347451</v>
+        <v>7347552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118433002</v>
+        <v>118433041</v>
       </c>
       <c r="B4" t="n">
-        <v>91788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724356</v>
+        <v>724351</v>
       </c>
       <c r="R4" t="n">
-        <v>7347531</v>
+        <v>7347536</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118433745</v>
+        <v>118433002</v>
       </c>
       <c r="B5" t="n">
-        <v>90460</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>724240</v>
+        <v>724356</v>
       </c>
       <c r="R5" t="n">
-        <v>7347532</v>
+        <v>7347531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118434082</v>
+        <v>118433170</v>
       </c>
       <c r="B6" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,42 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>724058</v>
+        <v>724323</v>
       </c>
       <c r="R6" t="n">
-        <v>7347655</v>
+        <v>7347671</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-07-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118433318</v>
+        <v>118434175</v>
       </c>
       <c r="B7" t="n">
-        <v>78493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>724240</v>
+        <v>724082</v>
       </c>
       <c r="R7" t="n">
-        <v>7347597</v>
+        <v>7347746</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,50 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118432971</v>
+        <v>118433318</v>
       </c>
       <c r="B8" t="n">
-        <v>79082</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>724346</v>
+        <v>724240</v>
       </c>
       <c r="R8" t="n">
-        <v>7347525</v>
+        <v>7347597</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1402,50 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118433505</v>
+        <v>118432837</v>
       </c>
       <c r="B9" t="n">
-        <v>97876</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>724216</v>
+        <v>724298</v>
       </c>
       <c r="R9" t="n">
-        <v>7347555</v>
+        <v>7347451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1504,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118433041</v>
+        <v>118432323</v>
       </c>
       <c r="B10" t="n">
-        <v>89584</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,34 +1462,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>724351</v>
+        <v>724102</v>
       </c>
       <c r="R10" t="n">
-        <v>7347536</v>
+        <v>7347410</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,6 +1530,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,50 +1561,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118433170</v>
+        <v>118432610</v>
       </c>
       <c r="B11" t="n">
-        <v>91788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ridok (Ridok), Lu lm</t>
+          <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>724323</v>
+        <v>724298</v>
       </c>
       <c r="R11" t="n">
-        <v>7347671</v>
+        <v>7347451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,15 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118432610</v>
+        <v>118434082</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,26 +1695,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ridok, Ridok, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>724298</v>
+        <v>724058</v>
       </c>
       <c r="R12" t="n">
-        <v>7347451</v>
+        <v>7347655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,6 +1748,11 @@
           <t>2024-07-14</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1816,6 +1774,517 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>118434322</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ridok, Ridok, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>724025</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7347547</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118434352</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ridok, Ridok, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>724032</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7347525</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118434205</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ridok, Ridok, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>724082</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7347746</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118433505</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ridok, Ridok, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>724216</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7347555</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118432971</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ridok, Ridok, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>724346</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7347525</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28052-2024 artfynd.xlsx
+++ b/artfynd/A 28052-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433745</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433339</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433041</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433002</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433170</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434175</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433318</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432837</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432323</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,6 +1714,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432610</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434082</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434322</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434352</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118434205</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2188,6 +2263,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118433505</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,8 +2365,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118432971</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>